--- a/docentes/González Altamirano Victorino Juventino - Estadisticos 20231.xlsx
+++ b/docentes/González Altamirano Victorino Juventino - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="65">
   <si>
     <t>Mat</t>
   </si>
@@ -85,118 +85,133 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>PANZO</t>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>OREA</t>
   </si>
   <si>
     <t>COBOS</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>PALOMINO</t>
-  </si>
-  <si>
-    <t>BELLO</t>
-  </si>
-  <si>
-    <t>YOPIHUA</t>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>LOBATO</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>MOLINA</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>PRADO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>AVALOS</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>NOLASCO</t>
   </si>
   <si>
     <t>ROJAS</t>
   </si>
   <si>
-    <t>JERONIMO</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
-    <t>NOLASCO</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
+    <t>MIXCOHUA</t>
+  </si>
+  <si>
+    <t>ALFONSO</t>
   </si>
   <si>
     <t>COLOHUA</t>
   </si>
   <si>
-    <t>PRADO</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>ACOSTA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>LUIS FERNANDO</t>
-  </si>
-  <si>
-    <t>LUIS</t>
-  </si>
-  <si>
-    <t>SHERLIN</t>
+    <t>ARACELY</t>
+  </si>
+  <si>
+    <t>ANETTE</t>
+  </si>
+  <si>
+    <t>BARUCH BOSET</t>
+  </si>
+  <si>
+    <t>GIOVANNI</t>
+  </si>
+  <si>
+    <t>LUIS FELIPE</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
   </si>
   <si>
     <t>YOLET</t>
   </si>
   <si>
-    <t>LEONEL FELIPE</t>
-  </si>
-  <si>
     <t>DAVID</t>
   </si>
   <si>
-    <t>ABDIEL NOE</t>
+    <t>PATRICIO</t>
+  </si>
+  <si>
+    <t>FABIAN ALEJANDRO</t>
+  </si>
+  <si>
+    <t>ERIK OMAR</t>
+  </si>
+  <si>
+    <t>VICTOR MANUEL</t>
+  </si>
+  <si>
+    <t>JOSUE GUSTAVO</t>
   </si>
   <si>
     <t>NAHUM HIRAM</t>
   </si>
   <si>
-    <t>ANETTE</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>MIGUEL ANTONIO</t>
-  </si>
-  <si>
-    <t>AARON MIGUEL</t>
-  </si>
-  <si>
-    <t>JOSUE</t>
-  </si>
-  <si>
-    <t>LUZ MARIA</t>
+    <t>ERIK</t>
   </si>
 </sst>
 </file>
@@ -724,7 +739,7 @@
         <v>14</v>
       </c>
       <c r="C7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -733,13 +748,13 @@
         <v>2</v>
       </c>
       <c r="F7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G7">
-        <v>94.59</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H7">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -818,16 +833,19 @@
         <v>29</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>29</v>
       </c>
-      <c r="E2">
-        <v>29</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
       <c r="G2">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>6.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -841,16 +859,19 @@
         <v>42</v>
       </c>
       <c r="D3">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>90.48</v>
+      </c>
+      <c r="H3">
+        <v>7.2</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -864,16 +885,19 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>94.44</v>
+      </c>
+      <c r="H4">
+        <v>6.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -887,16 +911,19 @@
         <v>44</v>
       </c>
       <c r="D5">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>81.81999999999999</v>
+      </c>
+      <c r="H5">
+        <v>6.6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -910,16 +937,19 @@
         <v>32</v>
       </c>
       <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
         <v>32</v>
       </c>
-      <c r="E6">
-        <v>32</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
       <c r="G6">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H6">
+        <v>6.2</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -930,19 +960,22 @@
         <v>14</v>
       </c>
       <c r="C7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D7">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>94.73999999999999</v>
+      </c>
+      <c r="H7">
+        <v>7.3</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -956,16 +989,19 @@
         <v>24</v>
       </c>
       <c r="D8">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="H8">
+        <v>5.7</v>
       </c>
     </row>
   </sheetData>
@@ -1021,16 +1057,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>75.86</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>6.8</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1047,16 +1083,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G3">
-        <v>92.86</v>
+        <v>90.48</v>
       </c>
       <c r="H3">
-        <v>7.2</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1073,16 +1109,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G4">
-        <v>80.56</v>
+        <v>94.44</v>
       </c>
       <c r="H4">
-        <v>6.8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1099,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G5">
-        <v>79.55</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H5">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1125,16 +1161,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="G6">
-        <v>78.13</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>6.2</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1145,7 +1181,7 @@
         <v>14</v>
       </c>
       <c r="C7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -1154,13 +1190,13 @@
         <v>2</v>
       </c>
       <c r="F7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G7">
-        <v>94.59</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H7">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1177,16 +1213,16 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G8">
-        <v>54.17</v>
+        <v>50</v>
       </c>
       <c r="H8">
-        <v>5.7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1196,7 +1232,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1228,22 +1264,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920009</v>
+        <v>22330051920190</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1251,22 +1287,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920017</v>
+        <v>22330051920098</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1274,22 +1310,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920322</v>
+        <v>22330051920108</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1297,22 +1333,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920007</v>
+        <v>22330051920284</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1320,22 +1356,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920184</v>
+        <v>22330051920053</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1343,7 +1379,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920188</v>
+        <v>22330051920054</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
@@ -1352,13 +1388,13 @@
         <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1366,22 +1402,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920180</v>
+        <v>22330051920061</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1389,22 +1425,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920200</v>
+        <v>21330051920053</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1412,114 +1448,114 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920098</v>
+        <v>21330051920007</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920054</v>
+        <v>22330051920188</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920038</v>
+        <v>21330051920197</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D12" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920043</v>
+        <v>22330051920413</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920292</v>
+        <v>22330051920192</v>
       </c>
       <c r="B14" t="s">
         <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="D14" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1527,24 +1563,93 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920203</v>
+        <v>22330051920193</v>
       </c>
       <c r="B15" t="s">
         <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="D15" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>22330051920356</v>
+      </c>
+      <c r="B16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" t="s">
+        <v>62</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>22330051920200</v>
+      </c>
+      <c r="B17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" t="s">
+        <v>63</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>22330051920202</v>
+      </c>
+      <c r="B18" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" t="s">
+        <v>47</v>
+      </c>
+      <c r="D18" t="s">
+        <v>64</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Altamirano Victorino Juventino - Estadisticos 20231.xlsx
+++ b/docentes/González Altamirano Victorino Juventino - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="66">
   <si>
     <t>Mat</t>
   </si>
@@ -94,39 +94,42 @@
     <t>ORTIZ</t>
   </si>
   <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>OREA</t>
+  </si>
+  <si>
+    <t>COBOS</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>LOBATO</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>MOLINA</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
     <t>VASQUEZ</t>
   </si>
   <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>OREA</t>
-  </si>
-  <si>
-    <t>COBOS</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>LOBATO</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>MOLINA</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
@@ -139,12 +142,12 @@
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>AVALOS</t>
-  </si>
-  <si>
     <t>ANTONIO</t>
   </si>
   <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
@@ -172,9 +175,6 @@
     <t>BARUCH BOSET</t>
   </si>
   <si>
-    <t>GIOVANNI</t>
-  </si>
-  <si>
     <t>LUIS FELIPE</t>
   </si>
   <si>
@@ -182,6 +182,9 @@
   </si>
   <si>
     <t>DANIELA</t>
+  </si>
+  <si>
+    <t>CLAUDIA PAOLA</t>
   </si>
   <si>
     <t>JOSE MANUEL</t>
@@ -1270,10 +1273,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1293,10 +1296,10 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1316,10 +1319,10 @@
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1333,22 +1336,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920284</v>
+        <v>22330051920053</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1356,16 +1359,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920053</v>
+        <v>22330051920054</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1379,16 +1382,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920054</v>
+        <v>22330051920061</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1402,16 +1405,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920061</v>
+        <v>22330051920212</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1431,10 +1434,10 @@
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1454,10 +1457,10 @@
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1477,10 +1480,10 @@
         <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1500,10 +1503,10 @@
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1526,7 +1529,7 @@
         <v>41</v>
       </c>
       <c r="D13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1549,7 +1552,7 @@
         <v>23</v>
       </c>
       <c r="D14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1572,7 +1575,7 @@
         <v>31</v>
       </c>
       <c r="D15" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1592,10 +1595,10 @@
         <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1612,13 +1615,13 @@
         <v>22330051920200</v>
       </c>
       <c r="B17" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1635,13 +1638,13 @@
         <v>22330051920202</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D18" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>

--- a/docentes/González Altamirano Victorino Juventino - Estadisticos 20231.xlsx
+++ b/docentes/González Altamirano Victorino Juventino - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="40">
   <si>
     <t>Mat</t>
   </si>
@@ -85,61 +85,34 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>JIMENEZ</t>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>JORGE</t>
+  </si>
+  <si>
+    <t>LUGO</t>
   </si>
   <si>
     <t>BAUTISTA</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>OREA</t>
-  </si>
-  <si>
-    <t>COBOS</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>LOBATO</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>MOLINA</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
     <t>PRADO</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
+    <t>LUNA</t>
   </si>
   <si>
     <t>ANTONIO</t>
@@ -148,73 +121,22 @@
     <t>RIVERA</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>NOLASCO</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>ARACELY</t>
+    <t>ZAYRA</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
   </si>
   <si>
     <t>ANETTE</t>
   </si>
   <si>
-    <t>BARUCH BOSET</t>
-  </si>
-  <si>
-    <t>LUIS FELIPE</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
+    <t>GUSTAVO</t>
   </si>
   <si>
     <t>DANIELA</t>
   </si>
   <si>
-    <t>CLAUDIA PAOLA</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>YOLET</t>
-  </si>
-  <si>
-    <t>DAVID</t>
-  </si>
-  <si>
-    <t>PATRICIO</t>
-  </si>
-  <si>
-    <t>FABIAN ALEJANDRO</t>
-  </si>
-  <si>
-    <t>ERIK OMAR</t>
-  </si>
-  <si>
-    <t>VICTOR MANUEL</t>
-  </si>
-  <si>
-    <t>JOSUE GUSTAVO</t>
-  </si>
-  <si>
-    <t>NAHUM HIRAM</t>
-  </si>
-  <si>
-    <t>ERIK</t>
+    <t>DIEGO</t>
   </si>
 </sst>
 </file>
@@ -995,13 +917,13 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F8">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G8">
-        <v>50</v>
+        <v>54.17</v>
       </c>
       <c r="H8">
         <v>5.7</v>
@@ -1069,7 +991,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>8.1</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1086,16 +1008,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G3">
-        <v>90.48</v>
+        <v>92.86</v>
       </c>
       <c r="H3">
-        <v>7.9</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1112,16 +1034,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G4">
-        <v>94.44</v>
+        <v>91.67</v>
       </c>
       <c r="H4">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1147,7 +1069,7 @@
         <v>81.81999999999999</v>
       </c>
       <c r="H5">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1173,7 +1095,7 @@
         <v>100</v>
       </c>
       <c r="H6">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1199,7 +1121,7 @@
         <v>94.73999999999999</v>
       </c>
       <c r="H7">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1216,16 +1138,16 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G8">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H8">
-        <v>6</v>
+        <v>6.9</v>
       </c>
     </row>
   </sheetData>
@@ -1235,7 +1157,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1267,22 +1189,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920190</v>
+        <v>22330051920100</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1290,16 +1212,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920098</v>
+        <v>22330051920105</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1313,16 +1235,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920108</v>
+        <v>22330051920098</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1331,44 +1253,44 @@
         <v>10</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920053</v>
+        <v>22330051920386</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920054</v>
+        <v>22330051920061</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1377,21 +1299,21 @@
         <v>12</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920061</v>
+        <v>22330051920334</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1400,259 +1322,6 @@
         <v>12</v>
       </c>
       <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>22330051920212</v>
-      </c>
-      <c r="B8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" t="s">
-        <v>42</v>
-      </c>
-      <c r="D8" t="s">
-        <v>55</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920053</v>
-      </c>
-      <c r="B9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" t="s">
-        <v>43</v>
-      </c>
-      <c r="D9" t="s">
-        <v>56</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920007</v>
-      </c>
-      <c r="B10" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D10" t="s">
-        <v>57</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920188</v>
-      </c>
-      <c r="B11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" t="s">
-        <v>58</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920197</v>
-      </c>
-      <c r="B12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" t="s">
-        <v>46</v>
-      </c>
-      <c r="D12" t="s">
-        <v>59</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>15</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920413</v>
-      </c>
-      <c r="B13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" t="s">
-        <v>41</v>
-      </c>
-      <c r="D13" t="s">
-        <v>60</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>15</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>22330051920192</v>
-      </c>
-      <c r="B14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" t="s">
-        <v>61</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>15</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>22330051920193</v>
-      </c>
-      <c r="B15" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" t="s">
-        <v>31</v>
-      </c>
-      <c r="D15" t="s">
-        <v>62</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>22330051920356</v>
-      </c>
-      <c r="B16" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" t="s">
-        <v>47</v>
-      </c>
-      <c r="D16" t="s">
-        <v>63</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>15</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>22330051920200</v>
-      </c>
-      <c r="B17" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" t="s">
-        <v>48</v>
-      </c>
-      <c r="D17" t="s">
-        <v>64</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>15</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>22330051920202</v>
-      </c>
-      <c r="B18" t="s">
-        <v>37</v>
-      </c>
-      <c r="C18" t="s">
-        <v>48</v>
-      </c>
-      <c r="D18" t="s">
-        <v>65</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>15</v>
-      </c>
-      <c r="G18">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Altamirano Victorino Juventino - Estadisticos 20231.xlsx
+++ b/docentes/González Altamirano Victorino Juventino - Estadisticos 20231.xlsx
@@ -991,7 +991,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>7.4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1017,7 +1017,7 @@
         <v>92.86</v>
       </c>
       <c r="H3">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1043,7 +1043,7 @@
         <v>91.67</v>
       </c>
       <c r="H4">
-        <v>7.1</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1069,7 +1069,7 @@
         <v>81.81999999999999</v>
       </c>
       <c r="H5">
-        <v>6.7</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1095,7 +1095,7 @@
         <v>100</v>
       </c>
       <c r="H6">
-        <v>7.7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1121,7 +1121,7 @@
         <v>94.73999999999999</v>
       </c>
       <c r="H7">
-        <v>7.2</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1147,7 +1147,7 @@
         <v>100</v>
       </c>
       <c r="H8">
-        <v>6.9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/González Altamirano Victorino Juventino - Estadisticos 20231.xlsx
+++ b/docentes/González Altamirano Victorino Juventino - Estadisticos 20231.xlsx
@@ -991,7 +991,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>10</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1017,7 +1017,7 @@
         <v>92.86</v>
       </c>
       <c r="H3">
-        <v>9.6</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1043,7 +1043,7 @@
         <v>91.67</v>
       </c>
       <c r="H4">
-        <v>9.6</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1069,7 +1069,7 @@
         <v>81.81999999999999</v>
       </c>
       <c r="H5">
-        <v>9.1</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1095,7 +1095,7 @@
         <v>100</v>
       </c>
       <c r="H6">
-        <v>10</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1121,7 +1121,7 @@
         <v>94.73999999999999</v>
       </c>
       <c r="H7">
-        <v>9.699999999999999</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1147,7 +1147,7 @@
         <v>100</v>
       </c>
       <c r="H8">
-        <v>10</v>
+        <v>6.9</v>
       </c>
     </row>
   </sheetData>
